--- a/artfynd/A 42590-2023 artfynd.xlsx
+++ b/artfynd/A 42590-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42590-2023 artfynd.xlsx
+++ b/artfynd/A 42590-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74387714</v>
+        <v>74387707</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartbäcksudden, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>377322.8570504078</v>
+        <v>377359</v>
       </c>
       <c r="R2" t="n">
-        <v>6700317.785605665</v>
+        <v>6700343</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +743,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74387707</v>
+        <v>74387703</v>
       </c>
       <c r="B3" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>377358.8679862526</v>
+        <v>377484</v>
       </c>
       <c r="R3" t="n">
-        <v>6700343.256730537</v>
+        <v>6700546</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +840,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,19 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74387710</v>
+        <v>74387705</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -944,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377335.9513292931</v>
+        <v>377439</v>
       </c>
       <c r="R4" t="n">
-        <v>6700295.101270344</v>
+        <v>6700515</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,19 +937,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,19 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74387708</v>
+        <v>74387706</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1056,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377359.1361964368</v>
+        <v>377428</v>
       </c>
       <c r="R5" t="n">
-        <v>6700278.00659248</v>
+        <v>6700519</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,19 +1034,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,55 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74387704</v>
+        <v>74387708</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svartbäcksudden, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377465.2049432121</v>
+        <v>377359</v>
       </c>
       <c r="R6" t="n">
-        <v>6700472.116744679</v>
+        <v>6700278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,19 +1131,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,19 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74387711</v>
+        <v>74387710</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1285,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>377332.9205706997</v>
+        <v>377336</v>
       </c>
       <c r="R7" t="n">
-        <v>6700337.215058203</v>
+        <v>6700295</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,19 +1228,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74387703</v>
+        <v>74387711</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1397,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377484.0416458471</v>
+        <v>377333</v>
       </c>
       <c r="R8" t="n">
-        <v>6700546.107721972</v>
+        <v>6700337</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,19 +1325,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,6 +1351,210 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>74387704</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svartbäcksudden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>377465</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6700472</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vitsand</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-11-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-11-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>74387714</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svartbäcksudden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>377323</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6700318</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vitsand</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-11-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-11-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42590-2023 artfynd.xlsx
+++ b/artfynd/A 42590-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387707</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387703</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387705</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387706</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387708</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387710</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387711</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387704</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,8 +1600,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387714</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>